--- a/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangdayou\Desktop\yudao\ruoyi-vue-pro\yudao-module-reagent\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EEA312-6737-49CF-B164-32F739DE6713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CFD188-4EEC-43D0-979F-00BF04E0F5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="570" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交接单" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -49,7 +49,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>jx:each(items="items" var="item" lastCell="I15")</t>
+          <t>jx:each(items="items" var="item" lastCell="I14")</t>
         </r>
       </text>
     </comment>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>Reagent Handover Sheet 试剂交接单 - 外寄</t>
   </si>
@@ -99,9 +99,6 @@
     <t/>
   </si>
   <si>
-    <t>收发信息</t>
-  </si>
-  <si>
     <t>发货单位:</t>
   </si>
   <si>
@@ -195,53 +192,215 @@
     <t>${item.lotNo}</t>
   </si>
   <si>
+    <t>${item.storageTemp}</t>
+  </si>
+  <si>
+    <t>${item.expirationDate}</t>
+  </si>
+  <si>
+    <t>以下由收货方填写 (Filled by Receiver)</t>
+  </si>
+  <si>
+    <t>试剂到达时是否处于合适储存条件？</t>
+  </si>
+  <si>
+    <t>□ 是 (Yes)</t>
+  </si>
+  <si>
+    <t>□ 否 (No) → 详细说明:</t>
+  </si>
+  <si>
+    <t>试剂到达时是否有损坏或缺失？</t>
+  </si>
+  <si>
+    <t>□ 否 (No)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此表为随货文件，签收后请将此回执的扫描件发送至邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>: jhsh_sample@accurantbio.com</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>${creatorTime}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${creator} </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>${item.quantityShipped}</t>
-  </si>
-  <si>
-    <t>${item.storageTemp}</t>
-  </si>
-  <si>
-    <t>${item.expirationDate}</t>
-  </si>
-  <si>
-    <t>制单人/日期:</t>
-  </si>
-  <si>
-    <t>${creator} / ${creatorTime}</t>
-  </si>
-  <si>
-    <t>以下由收货方填写 (Filled by Receiver)</t>
-  </si>
-  <si>
-    <t>试剂到达时是否处于合适储存条件？</t>
-  </si>
-  <si>
-    <t>□ 是 (Yes)</t>
-  </si>
-  <si>
-    <t>□ 否 (No) → 详细说明:</t>
-  </si>
-  <si>
-    <t>试剂到达时是否有损坏或缺失？</t>
-  </si>
-  <si>
-    <t>□ 是 (Yes) → 详细说明:</t>
-  </si>
-  <si>
-    <t>□ 否 (No)</t>
-  </si>
-  <si>
-    <t>接收人签名/日期:</t>
-  </si>
-  <si>
-    <t>注: 此表为随货文件，签收后请将此回执的扫描件发送至邮箱: jhsh_sample@accurantbio.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Yes) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>制单人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接收人签名</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -260,19 +419,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -296,6 +442,71 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -311,7 +522,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -334,51 +545,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,8 +1109,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
@@ -711,309 +1123,403 @@
     <col min="9" max="9" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="29"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="2" t="s">
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="2" t="s">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="2" t="s">
+      <c r="F7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="B8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="2" t="s">
+      <c r="F8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75">
+      <c r="A10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="I13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:9" ht="30.75" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="I14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="5" t="s">
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="40"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+    </row>
+    <row r="16" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="30" customHeight="1">
+      <c r="A18" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+    </row>
+    <row r="19" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A19" s="33" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="E19" s="5"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="H19" s="6"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" ht="33">
+      <c r="A20" s="33" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="H20" s="10"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A22" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="24">
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A15:I15"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A11:I12"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F10:I10"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangdayou\Desktop\yudao\ruoyi-vue-pro\yudao-module-reagent\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CFD188-4EEC-43D0-979F-00BF04E0F5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB05173-512B-43FE-A1E4-1E93BEF2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="570" windowWidth="23040" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交接单" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -49,7 +49,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>jx:each(items="items" var="item" lastCell="I14")</t>
+          <t>jx:each(items="items" var="item" lastCell="I13")</t>
         </r>
       </text>
     </comment>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>Reagent Handover Sheet 试剂交接单 - 外寄</t>
   </si>
@@ -78,12 +78,6 @@
     <t>${projectNo}</t>
   </si>
   <si>
-    <t>运费结算方式:</t>
-  </si>
-  <si>
-    <t>${freightSettlement}</t>
-  </si>
-  <si>
     <t>运输温度:</t>
   </si>
   <si>
@@ -175,15 +169,6 @@
   </si>
   <si>
     <t>${item.reagentName}</t>
-  </si>
-  <si>
-    <t>${item.basId}</t>
-  </si>
-  <si>
-    <t>${item.vendor}</t>
-  </si>
-  <si>
-    <t>${item.content}</t>
   </si>
   <si>
     <t>${item.catNo}</t>
@@ -395,12 +380,24 @@
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>${item.content}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.brand}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.basNo}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -477,11 +474,6 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -714,25 +706,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -777,20 +760,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,8 +1101,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
@@ -1123,399 +1115,378 @@
     <col min="9" max="9" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" customHeight="1">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="32"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="37" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75">
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75">
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
+      <c r="B6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
+        <v>13</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75">
+        <v>17</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
+        <v>21</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="B9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75">
-      <c r="A9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75">
-      <c r="A10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="39" t="s">
+      <c r="B12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="1" t="s">
+    </row>
+    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="B13" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="30.75" customHeight="1">
-      <c r="A14" s="15" t="s">
+      <c r="F13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="G13" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="I13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="15" t="s">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+    </row>
+    <row r="15" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+    </row>
+    <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="E18" s="5"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.2">
+      <c r="A19" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" ht="30" customHeight="1">
-      <c r="A18" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-    </row>
-    <row r="19" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A19" s="33" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" ht="33">
-      <c r="A20" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="2"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="26"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A23:I23"/>
+  <mergeCells count="22">
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A11:I12"/>
+    <mergeCell ref="A10:I11"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:I16"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F10:I10"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangdayou\Desktop\yudao\ruoyi-vue-pro\yudao-module-reagent\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB05173-512B-43FE-A1E4-1E93BEF2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95905619-66BB-41C9-898B-64E44573DE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="150" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交接单" sheetId="1" r:id="rId1"/>
@@ -201,41 +201,6 @@
     <t>□ 否 (No)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>此表为随货文件，签收后请将此回执的扫描件发送至邮箱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>: jhsh_sample@accurantbio.com</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>${creatorTime}</t>
   </si>
   <si>
@@ -390,6 +355,41 @@
   </si>
   <si>
     <t>${item.basNo}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此表为随货文件，签收后请将此回执的扫描件发送至邮箱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>:  ${consignorEmail}</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -718,62 +718,62 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1116,179 +1116,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="E6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="E9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
     </row>
     <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1324,13 +1324,13 @@
         <v>36</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>37</v>
@@ -1339,7 +1339,7 @@
         <v>38</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>39</v>
@@ -1349,30 +1349,30 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
     </row>
     <row r="15" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="39"/>
       <c r="D15" s="40"/>
       <c r="E15" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="39"/>
       <c r="H15" s="39"/>
@@ -1383,24 +1383,24 @@
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
     </row>
     <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="12" t="s">
         <v>43</v>
       </c>
@@ -1413,13 +1413,13 @@
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="8"/>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="21" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
@@ -1443,7 +1443,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -1451,20 +1451,26 @@
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="23"/>
+      <c r="A22" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A18:C18"/>
@@ -1481,12 +1487,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="F15:I15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
+++ b/yudao-module-reagent/src/main/resources/templates/reagent-shipment-print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangdayou\Desktop\yudao\ruoyi-vue-pro\yudao-module-reagent\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95905619-66BB-41C9-898B-64E44573DE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEEED22-811A-4863-B966-8338D4DC7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="150" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交接单" sheetId="1" r:id="rId1"/>
@@ -60,18 +60,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
-    <t>Reagent Handover Sheet 试剂交接单 - 外寄</t>
-  </si>
-  <si>
-    <t>以下由发货方填写 (Filled by Shipper)</t>
-  </si>
-  <si>
     <t>发货日期:</t>
   </si>
   <si>
-    <t>${shipmentDate}</t>
-  </si>
-  <si>
     <t>项目号:</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>${hasTempLogger}</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>发货单位:</t>
   </si>
   <si>
@@ -108,9 +96,6 @@
     <t>发货地址:</t>
   </si>
   <si>
-    <t>${consignorAddress}</t>
-  </si>
-  <si>
     <t>接收地址:</t>
   </si>
   <si>
@@ -138,36 +123,6 @@
     <t>${receiverPhone}</t>
   </si>
   <si>
-    <t>试剂信息 (Reagent Details)</t>
-  </si>
-  <si>
-    <t>试剂名称</t>
-  </si>
-  <si>
-    <t>BAS ID</t>
-  </si>
-  <si>
-    <t>供应商</t>
-  </si>
-  <si>
-    <t>规格/浓度</t>
-  </si>
-  <si>
-    <t>货号</t>
-  </si>
-  <si>
-    <t>批号</t>
-  </si>
-  <si>
-    <t>发货数量</t>
-  </si>
-  <si>
-    <t>储存温度</t>
-  </si>
-  <si>
-    <t>过期日期</t>
-  </si>
-  <si>
     <t>${item.reagentName}</t>
   </si>
   <si>
@@ -180,88 +135,15 @@
     <t>${item.storageTemp}</t>
   </si>
   <si>
-    <t>${item.expirationDate}</t>
-  </si>
-  <si>
-    <t>以下由收货方填写 (Filled by Receiver)</t>
-  </si>
-  <si>
-    <t>试剂到达时是否处于合适储存条件？</t>
-  </si>
-  <si>
-    <t>□ 是 (Yes)</t>
-  </si>
-  <si>
-    <t>□ 否 (No) → 详细说明:</t>
-  </si>
-  <si>
-    <t>试剂到达时是否有损坏或缺失？</t>
-  </si>
-  <si>
-    <t>□ 否 (No)</t>
-  </si>
-  <si>
     <t>${creatorTime}</t>
   </si>
   <si>
     <t xml:space="preserve">${creator} </t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>${item.quantityShipped}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>□</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Yes) → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>详细说明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -284,7 +166,7 @@
       </rPr>
       <t>:</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -306,58 +188,419 @@
       </rPr>
       <t>:</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.content}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.brand}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.basNo}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reagent Handover Sheet </t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="16"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂交接单</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The following shall be filled in by the shipper </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以下由发货方填写</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Do the reagents arrive in suitable storage conditions?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂到达时是否处于合适储存条件？</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any reagents arrived damaged or missing?
+试剂到达时是否有损坏或缺失？</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+日期</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Receiver Signature</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>接收人签名</t>
+      <t xml:space="preserve">
+接收人签名</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t>:</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>日期</t>
-    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${shipmentDate}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Yes) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>否</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (No)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>否</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (No) → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>详细说明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>${item.content}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>${item.brand}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>${item.basNo}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The following shall be filled in by the receiver </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以下由收货方填写</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Reagent Details </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试剂信息</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reagent Name
+试剂名称</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAS ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manufacturer
+制造商</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Size/Concentration
+规格/浓度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cat#
+货号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lot#
+批号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number
+发货数量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage temp
+储存温度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${item.expirationDate}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expiration date
+过期日期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -371,6 +614,8 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
@@ -387,17 +632,62 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>:  ${consignorEmail}</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note: This form is the document that comes with the goods. Please send the scanned copy of this receipt to the mailbox  ${consignorEmail}  after confirmation.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>□</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Yes)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>${consignorAddress}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -411,22 +701,11 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -499,6 +778,71 @@
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -660,74 +1004,59 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -739,49 +1068,94 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1101,8 +1475,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
@@ -1115,362 +1489,384 @@
     <col min="9" max="9" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" ht="23.25" customHeight="1">
+      <c r="A1" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="19"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="20"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A3" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="39"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="24"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="s">
+      <c r="B4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="14" t="s">
+      <c r="B5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="14" t="s">
+      <c r="B6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="F6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B7" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+      <c r="F9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A10" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="50"/>
+    </row>
+    <row r="12" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A12" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="25.5">
+      <c r="A13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="F13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="1"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="30" customHeight="1">
+      <c r="A17" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+    </row>
+    <row r="18" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A18" s="31" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="33">
+      <c r="A19" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A21" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="34"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-    </row>
-    <row r="15" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-    </row>
-    <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.2">
-      <c r="A19" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="21"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="F9:I9"/>
+  <mergeCells count="25">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A18:C18"/>
@@ -1487,8 +1883,14 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="F15:I15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="F9:I9"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
